--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Agevolazioni tributarie.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Agevolazioni tributarie.xlsx
@@ -133,7 +133,7 @@
     <t>Inserire una descrizione del servizio e delle tipologie di pagamenti che si potranno effettuare per il servizio.</t>
   </si>
   <si>
-    <t xml:space="preserve">Il servizio riguarda le agevolazioni tributarie, ovvero le eventuali riduzioni sull’importo da pagare per i tributi dovuti al Comune. 
+    <t xml:space="preserve">Il servizio riguarda le agevolazioni tributarie, ovvero le eventuali riduzioni sull’importo da pagare per i tributi dovuti al Comune.
 Tramite IO potrai:
 - ricevere informazioni sulle agevolazioni, su chi può accedervi e in che modalità;
 - ricevere comunicazioni e aggiornamenti sulle richieste di agevolazione presentate;
@@ -146,7 +146,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>Scopri le agevolazioni disponibili</t>
+    <t>Scopri le agevolazioni</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -332,7 +332,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve">. 
+      <t xml:space="preserve">.
 Hai tempo fino al </t>
     </r>
     <r>
@@ -518,7 +518,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> è stata accolta. 
+      <t xml:space="preserve"> è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -546,7 +546,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> non è stata accolta. 
+      <t xml:space="preserve"> non è stata accolta.
 Per ulteriori informazioni, [visita questo sito](URL).</t>
     </r>
   </si>
@@ -564,7 +564,7 @@
     </r>
   </si>
   <si>
-    <t>Fai richiesta</t>
+    <t>Invia richiesta</t>
   </si>
   <si>
     <t>-</t>
@@ -587,7 +587,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
